--- a/example.xlsx
+++ b/example.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -425,6 +425,8 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +455,16 @@
           <t>Ширина</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ширина на аппарат</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Заливка</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -470,6 +482,8 @@
       <c r="E2" t="n">
         <v>4</v>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,6 +501,8 @@
       <c r="E3" t="n">
         <v>4</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -508,6 +524,12 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>жёлтый</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -528,6 +550,12 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -540,6 +568,8 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -561,6 +591,12 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>жёлтый</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -582,6 +618,12 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>жёлтый</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -603,6 +645,12 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>жёлтый</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -628,6 +676,12 @@
       <c r="E10" t="n">
         <v>1</v>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -652,6 +706,12 @@
       </c>
       <c r="E11" t="n">
         <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -674,6 +734,12 @@
       <c r="E12" t="n">
         <v>1</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -695,6 +761,8 @@
       <c r="E13" t="n">
         <v>3</v>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -716,6 +784,35 @@
       <c r="E14" t="n">
         <v>1</v>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KL1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>РЕЛЕ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>НАСОСА</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>тег</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
